--- a/aq_files/0267.xlsx
+++ b/aq_files/0267.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Learning MCQs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,678 +413,468 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Details / Options</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>What is feature learning?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Manual feature selection</t>
+          <t>Everything in Python is:</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Automatic feature extraction</t>
+          <t>A) Object B) Function C) Variable D) None</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Data cleaning</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Model evaluation</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Feature learning is mainly used in?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Integer type example:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deep Learning</t>
+          <t>A) 10 B) '10' C) 10.5 D) None</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Databases</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Which model performs feature learning automatically?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linear Regression</t>
+          <t>Float example:</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Decision Tree</t>
+          <t>A) 10.5 B) 10 C) '10' D) None</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Neural Network</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>In deep learning, features are learned from?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>String example:</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raw data</t>
+          <t>A) 'hello' B) 10 C) 10.2 D) None</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Labels only</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Databases</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Low-level features include?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Edges</t>
+          <t>Boolean values:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Objects</t>
+          <t>A) True/False B) 1/0 C) Yes/No D) None</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Scenes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Concepts</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High-level features include?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edges</t>
+          <t>Write program to take input and print its type.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Textures</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Objects</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Pixels</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CNNs are used for?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Text processing</t>
+          <t>Write program to convert int to float.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Image feature learning</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Audio only</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Databases</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Feature hierarchy means?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Random features</t>
+          <t>Write program to convert string to int.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Layered features</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No features</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Manual features</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Which layer learns simple features?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>List is:</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hidden layers</t>
+          <t>A) Mutable B) Immutable C) None D) Both</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Activation functions help in?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Linear mapping</t>
+          <t>Tuple is:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Non-linearity</t>
+          <t>A) Immutable B) Mutable C) Both D) None</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Data storage</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sorting</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Which is a feature extractor?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Convolution layer</t>
+          <t>Write program to create list and print elements.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pooling layer</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dense layer</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pooling helps in?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Increase size</t>
+          <t>Write program to find length of list.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reduce dimensions</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Add noise</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Overfit</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Feature maps are outputs of?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pooling</t>
+          <t>Dictionary stores:</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Convolution</t>
+          <t>A) Key-value B) Only keys C) Only values D) None</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dense</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deep networks learn features in?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>One step</t>
+          <t>Set is:</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Multiple layers</t>
+          <t>A) Unique values B) Duplicate C) Ordered D) None</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No layers</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Random steps</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Transfer learning uses?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Random weights</t>
+          <t>Write program to count elements in dictionary.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pretrained features</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Manual coding</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Autoencoders are used for?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Write program to remove duplicates using set.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Feature learning</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sorting</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Searching</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unsupervised feature learning uses?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Labels</t>
+          <t>Write program to check type of variable dynamically.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No labels</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Only images</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Only text</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Feature learning reduces?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>None type represents:</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Manual effort</t>
+          <t>A) Null B) 0 C) False D) None</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Data size</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Which improves feature learning?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>More layers</t>
+          <t>Write program to assign multiple variables.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Less data</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No training</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Random input</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>End-to-end learning means?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Separate steps</t>
+          <t>Type() function does:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Learning features + task together</t>
+          <t>A) Returns type B) Converts C) Deletes D) None</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>No learning</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Manual steps</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
